--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486730_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486730_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0446</v>
+        <v>5.6981</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1812</v>
+        <v>6.636</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1365</v>
+        <v>-0.9379</v>
       </c>
       <c r="G2" t="n">
         <v>3.8457</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3847</v>
+        <v>0.2688</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4693</v>
+        <v>0.9855</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9153</v>
+        <v>-0.7167</v>
       </c>
       <c r="V2" t="n">
         <v>1.3905</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8769</v>
+        <v>4.2017</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3079</v>
+        <v>2.2563</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4311</v>
+        <v>1.9454</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2523</v>
+        <v>1.6529</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3586</v>
+        <v>-0.2145</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1063</v>
+        <v>1.8674</v>
       </c>
       <c r="J3" t="n">
-        <v>3.053</v>
+        <v>1.3711</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3589</v>
+        <v>0.0621</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6941000000000001</v>
+        <v>1.309</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8006</v>
+        <v>0.2818</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0003</v>
+        <v>-0.2766</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8003</v>
+        <v>0.5583</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4191</v>
+        <v>0.6413</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9927</v>
+        <v>0.5996</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5736</v>
+        <v>0.0417</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8193</v>
+        <v>0.9421</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4084</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8032</v>
+        <v>3.5957</v>
       </c>
       <c r="E4" t="n">
-        <v>1.684</v>
+        <v>3.853</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1192</v>
+        <v>-0.2572</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6529</v>
+        <v>2.2523</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2145</v>
+        <v>2.3586</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8674</v>
+        <v>-0.1063</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3711</v>
+        <v>3.053</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0621</v>
+        <v>2.3589</v>
       </c>
       <c r="L4" t="n">
-        <v>1.309</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2818</v>
+        <v>-0.8006</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2766</v>
+        <v>-0.0003</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5583</v>
+        <v>-0.8003</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2429</v>
+        <v>0.1379</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0273</v>
+        <v>0.5377</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2156</v>
+        <v>-0.3998</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9421</v>
+        <v>0.8193</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>1.2277</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6565</v>
+        <v>-0.4084</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6646</v>
+        <v>2.0065</v>
       </c>
       <c r="E5" t="n">
-        <v>5.5912</v>
+        <v>2.734</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9267</v>
+        <v>-0.7275</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4406</v>
+        <v>1.6272</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8905</v>
+        <v>1.2068</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4499</v>
+        <v>0.4205</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9248</v>
+        <v>2.1588</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0295</v>
+        <v>1.345</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8952</v>
+        <v>0.8138</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4841</v>
+        <v>-0.5316</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.139</v>
+        <v>-0.1382</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3451</v>
+        <v>-0.3934</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>5.0032</v>
+        <v>0.3793</v>
       </c>
       <c r="T5" t="n">
-        <v>4.4122</v>
+        <v>0.6411</v>
       </c>
       <c r="U5" t="n">
-        <v>0.591</v>
+        <v>-0.2618</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3931</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1851</v>
+        <v>0.8995</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5781</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4326</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0856</v>
+        <v>3.1091</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.653</v>
+        <v>-2.5723</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6272</v>
+        <v>0.4406</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2068</v>
+        <v>0.8905</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4205</v>
+        <v>-0.4499</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1588</v>
+        <v>1.9248</v>
       </c>
       <c r="K6" t="n">
-        <v>1.345</v>
+        <v>1.0295</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8138</v>
+        <v>0.8952</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5316</v>
+        <v>-1.4841</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1382</v>
+        <v>-0.139</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3934</v>
+        <v>-1.3451</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8054</v>
+        <v>1.8754</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9927</v>
+        <v>1.9301</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1873</v>
+        <v>-0.0546</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.3931</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8995</v>
+        <v>1.1851</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8995</v>
+        <v>-2.5781</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.717</v>
+        <v>0.1902</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5745</v>
+        <v>2.2711</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8575</v>
+        <v>-2.081</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0879</v>
@@ -1000,13 +1000,13 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1474</v>
+        <v>0.6206</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2959</v>
+        <v>0.9926</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1485</v>
+        <v>-0.372</v>
       </c>
       <c r="V7" t="n">
         <v>-0.694</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.067</v>
+        <v>-0.0422</v>
       </c>
       <c r="E8" t="n">
         <v>0.2062</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2732</v>
+        <v>-0.2484</v>
       </c>
       <c r="G8" t="n">
         <v>0.1647</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4248</v>
+        <v>-0.4</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6815</v>
+        <v>-0.2912</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.539</v>
+        <v>-1.1736</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8575</v>
+        <v>0.8824</v>
       </c>
       <c r="G9" t="n">
         <v>0.0743</v>
@@ -1156,13 +1156,13 @@
         <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5627</v>
+        <v>-0.1724</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4415</v>
+        <v>-0.076</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1212</v>
+        <v>-0.0964</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4607</v>
+        <v>-1.0193</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0018</v>
+        <v>0.319</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4626</v>
+        <v>-1.3384</v>
       </c>
       <c r="G11" t="n">
         <v>-0.426</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5793</v>
+        <v>-0.1379</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3032</v>
+        <v>0.6204</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8825</v>
+        <v>-0.7583</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4572</v>
+        <v>-2.2974</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1387</v>
+        <v>-1.1527</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3185</v>
+        <v>-1.1447</v>
       </c>
       <c r="G12" t="n">
         <v>-4.1538</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7944</v>
+        <v>0.3654</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4142</v>
+        <v>0.5718</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3803</v>
+        <v>-0.2065</v>
       </c>
       <c r="V12" t="n">
         <v>1.1049</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1873</v>
+        <v>-3.066</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8976</v>
+        <v>-2.1736</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2896</v>
+        <v>-0.8923</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5949</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5078</v>
+        <v>0.6135</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2753</v>
+        <v>0.9993</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7831</v>
+        <v>-0.3858</v>
       </c>
       <c r="V13" t="n">
         <v>-0.243</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.733600000000004</v>
+        <v>8.561299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>15.3124</v>
+        <v>16.1401</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.5789</v>
+        <v>-7.578799999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8255000000000008</v>
@@ -1516,10 +1516,10 @@
         <v>4.825499999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.651199999999999</v>
+        <v>-5.6512</v>
       </c>
       <c r="J14" t="n">
-        <v>9.943299999999997</v>
+        <v>9.943300000000001</v>
       </c>
       <c r="K14" t="n">
         <v>7.591400000000001</v>
@@ -1540,22 +1540,22 @@
         <v>4.827</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.723199999999999</v>
+        <v>-7.7232</v>
       </c>
       <c r="R14" t="n">
         <v>12.55</v>
       </c>
       <c r="S14" t="n">
-        <v>3.033299999999999</v>
+        <v>3.8609</v>
       </c>
       <c r="T14" t="n">
-        <v>6.753600000000001</v>
+        <v>7.581399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.7202</v>
+        <v>-3.7204</v>
       </c>
       <c r="V14" t="n">
-        <v>0.699</v>
+        <v>0.6990000000000004</v>
       </c>
       <c r="W14" t="n">
         <v>6.338900000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1639</v>
+        <v>3.1268</v>
       </c>
       <c r="E15" t="n">
-        <v>5.707</v>
+        <v>5.3968</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5431</v>
+        <v>-2.27</v>
       </c>
       <c r="G15" t="n">
         <v>5.6163</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0663</v>
+        <v>-0.1034</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1581</v>
+        <v>0.8478</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2244</v>
+        <v>-0.9512</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2277</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. KOWALSKI</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8568</v>
+        <v>2.5637</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6569</v>
+        <v>3.1512</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8</v>
+        <v>-0.5875</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2093</v>
+        <v>1.7358</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9510999999999999</v>
+        <v>0.7931</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1604</v>
+        <v>0.9427</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3907</v>
+        <v>3.2756</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2913</v>
+        <v>2.656</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0995</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1814</v>
+        <v>-1.5398</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2423</v>
+        <v>-1.8629</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0609</v>
+        <v>0.3232</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7377</v>
+        <v>0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0892</v>
+        <v>-1.1585</v>
       </c>
       <c r="R16" t="n">
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.629</v>
+        <v>-0.5929</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9853</v>
+        <v>-0.1936</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3563</v>
+        <v>-0.3993</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7563</v>
+        <v>1.2277</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3701</v>
+        <v>1.2277</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>R. KOWALSKI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9598</v>
+        <v>1.9798</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3238</v>
+        <v>3.8295</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.364</v>
+        <v>-1.8497</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7358</v>
+        <v>2.2093</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7931</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9427</v>
+        <v>3.1604</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2756</v>
+        <v>3.3907</v>
       </c>
       <c r="K17" t="n">
-        <v>2.656</v>
+        <v>0.2913</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6195000000000001</v>
+        <v>3.0995</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5398</v>
+        <v>-1.1814</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8629</v>
+        <v>-1.2423</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3232</v>
+        <v>0.0609</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1585</v>
+        <v>-3.0892</v>
       </c>
       <c r="R17" t="n">
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1967</v>
+        <v>-0.2481</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0209</v>
+        <v>1.1579</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1758</v>
+        <v>-1.406</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2277</v>
+        <v>1.7563</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>2.3701</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>C. TEASLEY JR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4058</v>
+        <v>0.5605</v>
       </c>
       <c r="E18" t="n">
-        <v>0.151</v>
+        <v>4.845</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2548</v>
+        <v>-4.2845</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2838</v>
+        <v>1.4915</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.607</v>
+        <v>1.1728</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3232</v>
+        <v>0.3187</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5659999999999999</v>
+        <v>3.28</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6067</v>
+        <v>2.6221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0407</v>
+        <v>0.6579</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2822</v>
+        <v>-1.7885</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0003</v>
+        <v>-1.4492</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2826</v>
+        <v>-0.3393</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4965</v>
+        <v>-0.8618</v>
       </c>
       <c r="T18" t="n">
-        <v>0.717</v>
+        <v>0.5304</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2205</v>
+        <v>-1.3922</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. TEASLEY JR</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3869</v>
+        <v>0.0956</v>
       </c>
       <c r="E19" t="n">
-        <v>4.121</v>
+        <v>-0.1593</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.508</v>
+        <v>0.2548</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4915</v>
+        <v>-0.2838</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1728</v>
+        <v>-0.607</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3187</v>
+        <v>0.3232</v>
       </c>
       <c r="J19" t="n">
-        <v>3.28</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6221</v>
+        <v>-0.6067</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6579</v>
+        <v>0.0407</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7885</v>
+        <v>0.2822</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4492</v>
+        <v>-0.0003</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3393</v>
+        <v>0.2826</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8092</v>
+        <v>0.1863</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1936</v>
+        <v>0.4067</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6156</v>
+        <v>-0.2205</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3672</v>
+        <v>-0.9039</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2138</v>
+        <v>0.1999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1534</v>
+        <v>-1.1037</v>
       </c>
       <c r="G20" t="n">
         <v>-1.0142</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7392</v>
+        <v>-0.2759</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2759</v>
+        <v>0.1378</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4633</v>
+        <v>-0.4136</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.505</v>
+        <v>-1.6043</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1486</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3564</v>
+        <v>-1.4558</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1713</v>
@@ -2092,13 +2092,13 @@
         <v>0.3862</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0718</v>
+        <v>-0.0275</v>
       </c>
       <c r="T21" t="n">
         <v>0.2756</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2038</v>
+        <v>-0.3031</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5985</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1906</v>
+        <v>-3.8567</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3125</v>
+        <v>-2.8296</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8781</v>
+        <v>-1.0271</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4103</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2318</v>
+        <v>-0.4343</v>
       </c>
       <c r="T22" t="n">
-        <v>0.772</v>
+        <v>0.2548</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5402</v>
+        <v>-0.6892</v>
       </c>
       <c r="V22" t="n">
         <v>1.8842</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. DEUS VERA</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8189</v>
+        <v>-4.2847</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3145</v>
+        <v>-2.8744</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5043</v>
+        <v>-1.4103</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6767</v>
+        <v>-2.671</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.2131</v>
+        <v>-1.5859</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4635</v>
+        <v>-1.0852</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.2412</v>
+        <v>-1.6012</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.2819</v>
+        <v>-1.0338</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0407</v>
+        <v>-0.5674</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4355</v>
+        <v>-1.0698</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0687</v>
+        <v>-0.5521</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5042</v>
+        <v>-0.5178</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7723</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5296</v>
+        <v>-0.6136</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7995</v>
+        <v>0.0205</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2699</v>
+        <v>-0.6341</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8995</v>
+        <v>-0.6138</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2856</v>
+        <v>-0.3282</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1851</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>R. DEUS VERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8515</v>
+        <v>-5.4105</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3915</v>
+        <v>-3.8316</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.46</v>
+        <v>-1.5788</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.671</v>
+        <v>-3.6767</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5859</v>
+        <v>-3.2131</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0852</v>
+        <v>-0.4635</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6012</v>
+        <v>-3.2412</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.0338</v>
+        <v>-3.2819</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5674</v>
+        <v>0.0407</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0698</v>
+        <v>-0.4355</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5521</v>
+        <v>0.0687</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5178</v>
+        <v>-0.5042</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3862</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1804</v>
+        <v>-0.062</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4966</v>
+        <v>0.2824</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6838</v>
+        <v>-0.3444</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6138</v>
+        <v>-0.8995</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3282</v>
+        <v>0.2856</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2856</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.7338</v>
+        <v>-7.7337</v>
       </c>
       <c r="E25" t="n">
-        <v>7.578800000000001</v>
+        <v>7.578900000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.3125</v>
+        <v>-15.3126</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8255999999999997</v>
+        <v>0.8256000000000019</v>
       </c>
       <c r="H25" t="n">
         <v>-4.8256</v>
@@ -2380,7 +2380,7 @@
         <v>10.7689</v>
       </c>
       <c r="K25" t="n">
-        <v>2.765800000000001</v>
+        <v>2.7658</v>
       </c>
       <c r="L25" t="n">
         <v>8.0032</v>
@@ -2389,13 +2389,13 @@
         <v>-9.9434</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.5914</v>
+        <v>-7.591400000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-2.352</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.826899999999999</v>
+        <v>-4.8269</v>
       </c>
       <c r="Q25" t="n">
         <v>-12.5502</v>
@@ -2404,10 +2404,10 @@
         <v>7.7231</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.0331</v>
+        <v>-3.0332</v>
       </c>
       <c r="T25" t="n">
-        <v>3.720499999999999</v>
+        <v>3.7203</v>
       </c>
       <c r="U25" t="n">
         <v>-6.7536</v>
